--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary_Quit.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary_Quit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E768A2-1410-400F-8705-771AFB7C7079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9213D56-FB0C-46C2-9078-5BF03664F76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -518,9 +518,6 @@
     <t>Tính thuế thử việc</t>
   </si>
   <si>
-    <t>Tăng ca miễn thuế</t>
-  </si>
-  <si>
     <t>Tổng thu nhập</t>
   </si>
   <si>
@@ -558,6 +555,10 @@
   </si>
   <si>
     <t>HT16</t>
+  </si>
+  <si>
+    <t>Tiền lương ngày thực trả
+Actual wage per day</t>
   </si>
 </sst>
 </file>
@@ -909,17 +910,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -943,6 +933,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1111,10 +1110,10 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1130,28 +1129,91 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1163,12 +1225,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1181,74 +1237,19 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma 2 2 2" xfId="2" xr:uid="{F56B0337-0F8B-4943-BF83-EA71CD031E4E}"/>
@@ -1656,7 +1657,11 @@
     <col min="51" max="52" width="9.140625" style="4"/>
     <col min="53" max="53" width="26.5703125" style="4" customWidth="1"/>
     <col min="54" max="54" width="23.28515625" style="4" customWidth="1"/>
-    <col min="55" max="16384" width="9.140625" style="4"/>
+    <col min="55" max="61" width="9.140625" style="4"/>
+    <col min="62" max="62" width="13.7109375" style="4" customWidth="1"/>
+    <col min="63" max="63" width="9.140625" style="4"/>
+    <col min="64" max="65" width="14" style="4" customWidth="1"/>
+    <col min="66" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1664,20 +1669,9 @@
         <v>1</v>
       </c>
       <c r="O1" s="4"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="100"/>
-      <c r="X1" s="100"/>
-      <c r="Y1" s="100"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="100"/>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="100"/>
-      <c r="AD1" s="100"/>
-      <c r="AE1" s="100"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="64"/>
+      <c r="AE1" s="4"/>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
@@ -1692,29 +1686,18 @@
       <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="72"/>
+      <c r="L2" s="93"/>
       <c r="M2" s="54">
         <f>BQ14</f>
         <v>0</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
-      <c r="Z2" s="100"/>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="100"/>
-      <c r="AD2" s="100"/>
-      <c r="AE2" s="100"/>
-      <c r="AF2" s="100"/>
-      <c r="AG2" s="100"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="64"/>
+      <c r="AE2" s="4"/>
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
@@ -1730,20 +1713,9 @@
         <v>3</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="T3" s="100"/>
-      <c r="U3" s="100"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="100"/>
-      <c r="X3" s="100"/>
-      <c r="Y3" s="100"/>
-      <c r="Z3" s="100"/>
-      <c r="AA3" s="100"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="100"/>
-      <c r="AD3" s="100"/>
-      <c r="AE3" s="100"/>
-      <c r="AF3" s="100"/>
-      <c r="AG3" s="100"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="64"/>
+      <c r="AE3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
@@ -1759,20 +1731,9 @@
         <v>4</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="100"/>
-      <c r="AD4" s="100"/>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="64"/>
+      <c r="AE4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
@@ -1783,25 +1744,14 @@
       <c r="AS4" s="4"/>
       <c r="AW4" s="4"/>
     </row>
-    <row r="5" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:79" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>5</v>
       </c>
       <c r="O5" s="4"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100"/>
-      <c r="V5" s="101"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="100"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
-      <c r="AC5" s="100"/>
-      <c r="AD5" s="100"/>
-      <c r="AE5" s="100"/>
-      <c r="AF5" s="100"/>
-      <c r="AG5" s="100"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="64"/>
+      <c r="AE5" s="4"/>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
@@ -1812,7 +1762,7 @@
       <c r="AS5" s="4"/>
       <c r="AW5" s="4"/>
     </row>
-    <row r="6" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:79" ht="24.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>6</v>
       </c>
@@ -1847,38 +1797,36 @@
         <v>54</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="101" t="s">
+      <c r="U6" s="4"/>
+      <c r="V6" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="100" t="s">
+      <c r="W6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="X6" s="100" t="s">
+      <c r="X6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Y6" s="100" t="s">
+      <c r="Y6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Z6" s="100" t="s">
+      <c r="Z6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AA6" s="100" t="s">
+      <c r="AA6" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AB6" s="100" t="s">
+      <c r="AB6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AC6" s="102"/>
-      <c r="AD6" s="100" t="s">
+      <c r="AC6"/>
+      <c r="AD6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AE6" s="100" t="s">
+      <c r="AE6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AF6" s="100"/>
-      <c r="AG6" s="100" t="s">
+      <c r="AG6" s="4" t="s">
         <v>82</v>
       </c>
       <c r="AI6" s="4" t="s">
@@ -1908,10 +1856,10 @@
         <v>138</v>
       </c>
       <c r="AW6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AX6" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BA6" s="4" t="s">
         <v>142</v>
@@ -1923,15 +1871,15 @@
         <v>55</v>
       </c>
       <c r="BH6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="BI6" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BJ6" s="4" t="s">
+      <c r="BK6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BM6" s="4" t="s">
+      <c r="BN6" s="4" t="s">
         <v>143</v>
       </c>
       <c r="BO6" s="4" t="s">
@@ -1944,7 +1892,7 @@
         <v>78</v>
       </c>
       <c r="BR6" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BS6" s="4" t="s">
         <v>60</v>
@@ -1959,13 +1907,13 @@
         <v>70</v>
       </c>
       <c r="BW6" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BX6" s="4" t="s">
         <v>76</v>
       </c>
       <c r="BY6" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BZ6" s="4" t="s">
         <v>71</v>
@@ -2014,46 +1962,46 @@
       <c r="S7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T7" s="100" t="s">
+      <c r="T7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="100" t="s">
+      <c r="U7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V7" s="101" t="s">
+      <c r="V7" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="W7" s="100" t="s">
+      <c r="W7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="100" t="s">
+      <c r="X7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="Y7" s="100" t="s">
+      <c r="Y7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="Z7" s="100" t="s">
+      <c r="Z7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA7" s="100" t="s">
+      <c r="AA7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AB7" s="100" t="s">
+      <c r="AB7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="AC7" s="100" t="s">
+      <c r="AC7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AD7" s="100" t="s">
+      <c r="AD7" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AE7" s="100" t="s">
+      <c r="AE7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AF7" s="100" t="s">
+      <c r="AF7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AG7" s="100" t="s">
+      <c r="AG7" s="4" t="s">
         <v>121</v>
       </c>
       <c r="AH7" s="4" t="s">
@@ -2106,10 +2054,10 @@
         <v>55</v>
       </c>
       <c r="BH7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI7" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="BI7" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2120,20 +2068,9 @@
         <v>48</v>
       </c>
       <c r="O8" s="4"/>
-      <c r="T8" s="100"/>
-      <c r="U8" s="100"/>
-      <c r="V8" s="101"/>
-      <c r="W8" s="100"/>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="100"/>
-      <c r="AA8" s="100"/>
-      <c r="AB8" s="100"/>
-      <c r="AC8" s="100"/>
-      <c r="AD8" s="100"/>
-      <c r="AE8" s="100"/>
-      <c r="AF8" s="100"/>
-      <c r="AG8" s="100"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="64"/>
+      <c r="AE8" s="4"/>
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4"/>
@@ -2147,10 +2084,10 @@
         <v>55</v>
       </c>
       <c r="BH8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI8" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="BI8" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,46 +2145,46 @@
       <c r="S9" s="4">
         <v>1</v>
       </c>
-      <c r="T9" s="100">
-        <v>1</v>
-      </c>
-      <c r="U9" s="100">
-        <v>1</v>
-      </c>
-      <c r="V9" s="101">
-        <v>1</v>
-      </c>
-      <c r="W9" s="100">
-        <v>1</v>
-      </c>
-      <c r="X9" s="100">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="100">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="100">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="100">
+      <c r="T9" s="4">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4">
+        <v>1</v>
+      </c>
+      <c r="V9" s="64">
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>1</v>
+      </c>
+      <c r="X9" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="4">
         <v>1</v>
       </c>
       <c r="AH9" s="4">
@@ -2297,7 +2234,7 @@
       </c>
       <c r="AW9" s="4"/>
     </row>
-    <row r="10" spans="1:79" ht="24.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10</v>
       </c>
@@ -2334,46 +2271,46 @@
       <c r="S10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="T10" s="100" t="s">
+      <c r="T10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="U10" s="100" t="s">
+      <c r="U10" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="V10" s="101" t="s">
+      <c r="V10" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="W10" s="100" t="s">
+      <c r="W10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="X10" s="100" t="s">
+      <c r="X10" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="Y10" s="100" t="s">
+      <c r="Y10" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="Z10" s="100" t="s">
+      <c r="Z10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AA10" s="100" t="s">
+      <c r="AA10" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AB10" s="100" t="s">
+      <c r="AB10" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="AC10" s="100" t="s">
+      <c r="AC10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AD10" s="100" t="s">
+      <c r="AD10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AE10" s="100" t="s">
+      <c r="AE10" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AF10" s="100" t="s">
+      <c r="AF10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AG10" s="100" t="s">
+      <c r="AG10" s="4" t="s">
         <v>121</v>
       </c>
       <c r="AH10" s="4" t="s">
@@ -2424,101 +2361,101 @@
       <c r="AW10" s="4"/>
     </row>
     <row r="11" spans="1:79" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="75" t="s">
+      <c r="B11" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="77" t="s">
+      <c r="G11" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="79" t="s">
+      <c r="H11" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="81" t="s">
+      <c r="I11" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81" t="s">
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="81"/>
-      <c r="P11" s="96" t="s">
+      <c r="O11" s="72"/>
+      <c r="P11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="98" t="s">
+      <c r="Q11" s="74"/>
+      <c r="R11" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="S11" s="99"/>
-      <c r="T11" s="81" t="s">
+      <c r="S11" s="76"/>
+      <c r="T11" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="75" t="s">
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="72"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="72"/>
+      <c r="AC11" s="72"/>
+      <c r="AD11" s="72"/>
+      <c r="AE11" s="72"/>
+      <c r="AF11" s="72"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="AI11" s="92" t="s">
+      <c r="AI11" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="AJ11" s="92"/>
-      <c r="AK11" s="92"/>
-      <c r="AL11" s="92"/>
-      <c r="AM11" s="92"/>
-      <c r="AN11" s="92"/>
-      <c r="AO11" s="92"/>
-      <c r="AP11" s="93" t="s">
+      <c r="AJ11" s="67"/>
+      <c r="AK11" s="67"/>
+      <c r="AL11" s="67"/>
+      <c r="AM11" s="67"/>
+      <c r="AN11" s="67"/>
+      <c r="AO11" s="67"/>
+      <c r="AP11" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="AQ11" s="87" t="s">
+      <c r="AQ11" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AR11" s="95"/>
-      <c r="AS11" s="95"/>
-      <c r="AT11" s="95"/>
-      <c r="AU11" s="95"/>
-      <c r="AV11" s="64" t="s">
+      <c r="AR11" s="71"/>
+      <c r="AS11" s="71"/>
+      <c r="AT11" s="71"/>
+      <c r="AU11" s="71"/>
+      <c r="AV11" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="AW11" s="87" t="s">
+      <c r="AW11" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX11" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="AX11" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="AY11" s="64" t="s">
+      <c r="AY11" s="82" t="s">
         <v>16</v>
       </c>
       <c r="AZ11" s="7"/>
-      <c r="BA11" s="66" t="s">
+      <c r="BA11" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="BB11" s="70" t="s">
+      <c r="BB11" s="102" t="s">
         <v>18</v>
       </c>
       <c r="BC11" s="8"/>
@@ -2533,56 +2470,58 @@
       <c r="BI11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BJ11" s="68" t="s">
+      <c r="BJ11" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK11" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="BK11" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="BL11" s="89" t="s">
+      <c r="BL11" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="BM11" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="BM11" s="90"/>
-      <c r="BN11" s="90"/>
-      <c r="BO11" s="91"/>
-      <c r="BP11" s="68" t="s">
+      <c r="BN11" s="85"/>
+      <c r="BO11" s="66"/>
+      <c r="BP11" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="BQ11" s="83" t="s">
+      <c r="BQ11" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="BR11" s="68" t="s">
+      <c r="BR11" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="BS11" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="BT11" s="91"/>
+      <c r="BU11" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="BV11" s="86"/>
+      <c r="BW11" s="92" t="s">
+        <v>159</v>
+      </c>
+      <c r="BX11" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="BS11" s="85" t="s">
-        <v>59</v>
-      </c>
-      <c r="BT11" s="85"/>
-      <c r="BU11" s="83" t="s">
-        <v>59</v>
-      </c>
-      <c r="BV11" s="83"/>
-      <c r="BW11" s="86" t="s">
-        <v>160</v>
-      </c>
-      <c r="BX11" s="84" t="s">
+      <c r="BY11" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="BY11" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="CA11" s="82" t="s">
+      <c r="CA11" s="89" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:79" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="74"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="80"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="99"/>
       <c r="I12" s="48" t="s">
         <v>20</v>
       </c>
@@ -2655,10 +2594,10 @@
       <c r="AF12" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="AG12" s="103" t="s">
+      <c r="AG12" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="AH12" s="76"/>
+      <c r="AH12" s="78"/>
       <c r="AI12" s="49">
         <v>1.5</v>
       </c>
@@ -2680,7 +2619,7 @@
       <c r="AO12" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AP12" s="94"/>
+      <c r="AP12" s="69"/>
       <c r="AQ12" s="46" t="s">
         <v>42</v>
       </c>
@@ -2696,13 +2635,13 @@
       <c r="AU12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="AV12" s="65"/>
-      <c r="AW12" s="88"/>
-      <c r="AX12" s="65"/>
-      <c r="AY12" s="65"/>
+      <c r="AV12" s="83"/>
+      <c r="AW12" s="81"/>
+      <c r="AX12" s="83"/>
+      <c r="AY12" s="83"/>
       <c r="AZ12" s="9"/>
-      <c r="BA12" s="67"/>
-      <c r="BB12" s="71"/>
+      <c r="BA12" s="101"/>
+      <c r="BB12" s="103"/>
       <c r="BC12" s="10" t="str">
         <f>+IF(C12="SK2","SK2",IF(C12="FACTORY A","SK1 Box",IF(C12="FACTORY D","SK1 Bag","Chia")))</f>
         <v>Chia</v>
@@ -2712,23 +2651,21 @@
         <f>+IF(BC12="SK1 Box","Box",IF(BC12="Seaman","Seaman","Bag"))</f>
         <v>Bag</v>
       </c>
-      <c r="BJ12" s="69"/>
-      <c r="BK12" s="69"/>
-      <c r="BL12" s="35" t="s">
+      <c r="BJ12" s="88"/>
+      <c r="BK12" s="80"/>
+      <c r="BL12" s="80"/>
+      <c r="BM12" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="BM12" s="35" t="s">
+      <c r="BN12" s="35" t="s">
         <v>92</v>
-      </c>
-      <c r="BN12" s="35" t="s">
-        <v>148</v>
       </c>
       <c r="BO12" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="BP12" s="69"/>
-      <c r="BQ12" s="83"/>
-      <c r="BR12" s="69"/>
+      <c r="BP12" s="80"/>
+      <c r="BQ12" s="86"/>
+      <c r="BR12" s="80"/>
       <c r="BS12" s="34">
         <v>1</v>
       </c>
@@ -2741,13 +2678,13 @@
       <c r="BV12" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="BW12" s="86"/>
-      <c r="BX12" s="84"/>
-      <c r="BY12" s="82"/>
+      <c r="BW12" s="92"/>
+      <c r="BX12" s="90"/>
+      <c r="BY12" s="89"/>
       <c r="BZ12" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="CA12" s="82"/>
+      <c r="CA12" s="89"/>
     </row>
     <row r="13" spans="1:79" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
@@ -2821,59 +2758,59 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T13" s="104">
+      <c r="T13" s="44">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U13" s="104">
+      <c r="U13" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V13" s="104">
+      <c r="V13" s="44">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W13" s="104">
+      <c r="W13" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X13" s="104">
+      <c r="X13" s="44">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y13" s="104">
+      <c r="Y13" s="44">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z13" s="104">
+      <c r="Z13" s="44">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA13" s="104">
+      <c r="AA13" s="44">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB13" s="104">
+      <c r="AB13" s="44">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC13" s="104">
+      <c r="AC13" s="44">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD13" s="104">
+      <c r="AD13" s="44">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE13" s="104">
+      <c r="AE13" s="44">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF13" s="104">
+      <c r="AF13" s="44">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG13" s="104">
+      <c r="AG13" s="44">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -2997,9 +2934,9 @@
         <f>(BT14)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="23" t="e">
-        <f>ROUND((M14/IF($M$2&gt;26,26,BQ14)/8*BT14)*0.3,0)</f>
-        <v>#DIV/0!</v>
+      <c r="S14" s="23">
+        <f>ROUND(BJ14/8*BT14*0.3,0)</f>
+        <v>0</v>
       </c>
       <c r="T14" s="23" t="e">
         <f>O14+Q14+S14</f>
@@ -3041,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="AF14" s="23">
-        <f>IF(AND(BX14="Female",BS14+BT14+BU14&gt;=13*8),1.5*M14/IF($M$2*8&gt;208,208,BQ14*8),0)</f>
+        <f>IF(AND(BX14="Female",BS14+BT14+BU14&gt;=13*8),1.5*BJ14/8,0)</f>
         <v>0</v>
       </c>
       <c r="AG14" s="30">
@@ -3069,9 +3006,9 @@
       <c r="AN14" s="24">
         <v>0</v>
       </c>
-      <c r="AO14" s="50" t="e">
-        <f>ROUND(M14/IF($M$2*8&gt;208,208,BQ14*8)*(AI14*1.5 + AJ14* 2 + AK14* 2.1 + AL14* 2.7 + AM14* 3 + AN14* 3.9),0)</f>
-        <v>#DIV/0!</v>
+      <c r="AO14" s="50">
+        <f>ROUND(BJ14/8*(AI14*1.5 + AJ14* 2 + AK14* 2.1 + AL14* 2.7 + AM14* 3 + AN14* 3.9),0)</f>
+        <v>0</v>
       </c>
       <c r="AP14" s="31" t="e">
         <f>ROUND(AH14+AO14,0)</f>
@@ -3086,8 +3023,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AS14" s="51" t="e">
-        <f>IF(BO14=1,IF(BK14&gt;11000000,BK14*10%,0),IF(BL14&gt;0,ROUND(IF(BL14&lt;5000000,BL14*0.05,IF(BL14&lt;10000000,BL14*0.1-250000,IF(BL14&lt;18000000,BL14*0.15-750000,IF(BL14&lt;32000000,BL14*0.2-1650000,IF(BL14&lt;52000000,BL14*0.25-3250000,IF(BL14&lt;80000000,BL14*0.3-5850000,BL14*0.35-9850000)))))),0),0))</f>
-        <v>#DIV/0!</v>
+        <f>IF(#REF!=1,IF(BL14&gt;11000000,BL14*10%,0),IF(BM14&gt;0,ROUND(IF(BM14&lt;5000000,BM14*0.05,IF(BM14&lt;10000000,BM14*0.1-250000,IF(BM14&lt;18000000,BM14*0.15-750000,IF(BM14&lt;32000000,BM14*0.2-1650000,IF(BM14&lt;52000000,BM14*0.25-3250000,IF(BM14&lt;80000000,BM14*0.3-5850000,BM14*0.35-9850000)))))),0),0))</f>
+        <v>#REF!</v>
       </c>
       <c r="AT14" s="23">
         <v>0</v>
@@ -3123,22 +3060,22 @@
         <v>58</v>
       </c>
       <c r="BJ14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK14" s="37" t="e">
+        <f>IF(N14&gt;0,O14/IF(N14&gt;26,26,N14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK14" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL14" s="37" t="e">
         <f>AP14 + BP14 - AQ14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BL14" s="4" t="e">
-        <f>BK14 - BN14 - U14 - BM14*4400000 - 11000000</f>
+      <c r="BM14" s="104" t="e">
+        <f>BL14-#REF!-U14-BN14*4400000-11000000 - ROUND(BJ14/8*(BT14*0.3+AI14*0.5+AJ14*1+AK14*1.1+AL14*1.7+AM14*2+AN14*2.9),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BM14" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN14" s="38" t="e">
-        <f>ROUND(M14/IF($M$2*8&gt;208,208,BQ14*8)*(BT14*0.3 + AI14*0.5 + AJ14* 1 + AK14* 1.1 + AL14* 1.7 + AM14* 2 + AN14* 2.9),0)</f>
-        <v>#DIV/0!</v>
+      <c r="BN14" s="4">
+        <v>0</v>
       </c>
       <c r="BO14" s="38"/>
       <c r="BP14" s="38">
@@ -3177,27 +3114,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A13:BE13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="35">
-    <mergeCell ref="AI11:AO11"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AU11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:AG11"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="BR11:BR12"/>
-    <mergeCell ref="AW11:AW12"/>
-    <mergeCell ref="AX11:AX12"/>
-    <mergeCell ref="BL11:BO11"/>
+  <mergeCells count="36">
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AY11:AY12"/>
+    <mergeCell ref="BA11:BA12"/>
+    <mergeCell ref="BP11:BP12"/>
+    <mergeCell ref="BB11:BB12"/>
     <mergeCell ref="BK11:BK12"/>
-    <mergeCell ref="BQ11:BQ12"/>
-    <mergeCell ref="CA11:CA12"/>
-    <mergeCell ref="BU11:BV11"/>
-    <mergeCell ref="BY11:BY12"/>
-    <mergeCell ref="BX11:BX12"/>
-    <mergeCell ref="BS11:BT11"/>
-    <mergeCell ref="BW11:BW12"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
@@ -3207,12 +3130,27 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:M11"/>
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AY11:AY12"/>
-    <mergeCell ref="BA11:BA12"/>
-    <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BB11:BB12"/>
+    <mergeCell ref="CA11:CA12"/>
+    <mergeCell ref="BU11:BV11"/>
+    <mergeCell ref="BY11:BY12"/>
+    <mergeCell ref="BX11:BX12"/>
+    <mergeCell ref="BS11:BT11"/>
+    <mergeCell ref="BW11:BW12"/>
+    <mergeCell ref="BR11:BR12"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="AX11:AX12"/>
+    <mergeCell ref="BM11:BN11"/>
+    <mergeCell ref="BL11:BL12"/>
+    <mergeCell ref="BQ11:BQ12"/>
     <mergeCell ref="BJ11:BJ12"/>
+    <mergeCell ref="AI11:AO11"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AU11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:AG11"/>
+    <mergeCell ref="AH11:AH12"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C11:C13 D13:AY13">

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary_Quit.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/MonthlySalary_Quit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9213D56-FB0C-46C2-9078-5BF03664F76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749B5515-8927-4B78-A20D-250BAEFF1CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$13:$BE$13</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="178">
   <si>
     <t>TT
 No.</t>
@@ -559,6 +570,54 @@
   <si>
     <t>Tiền lương ngày thực trả
 Actual wage per day</t>
+  </si>
+  <si>
+    <t>s43</t>
+  </si>
+  <si>
+    <t>s46</t>
+  </si>
+  <si>
+    <t>s47</t>
+  </si>
+  <si>
+    <t>s48</t>
+  </si>
+  <si>
+    <t>s49</t>
+  </si>
+  <si>
+    <t>s50</t>
+  </si>
+  <si>
+    <t>s51</t>
+  </si>
+  <si>
+    <t>s52</t>
+  </si>
+  <si>
+    <t>s53</t>
+  </si>
+  <si>
+    <t>s54</t>
+  </si>
+  <si>
+    <t>s55</t>
+  </si>
+  <si>
+    <t>s57</t>
+  </si>
+  <si>
+    <t>s58</t>
+  </si>
+  <si>
+    <t>s59</t>
+  </si>
+  <si>
+    <t>Số tiền phép năm</t>
+  </si>
+  <si>
+    <t>SoTienThanhToanPhepNamConLai</t>
   </si>
 </sst>
 </file>
@@ -952,7 +1011,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1138,6 +1197,75 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1153,9 +1281,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1168,34 +1293,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1204,52 +1308,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma 2 2 2" xfId="2" xr:uid="{F56B0337-0F8B-4943-BF83-EA71CD031E4E}"/>
@@ -1315,7 +1373,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>515470</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>261405</xdr:rowOff>
+      <xdr:rowOff>264580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1614,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CA14"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0" style="4" hidden="1" customWidth="1"/>
@@ -1659,12 +1717,14 @@
     <col min="54" max="54" width="23.28515625" style="4" customWidth="1"/>
     <col min="55" max="61" width="9.140625" style="4"/>
     <col min="62" max="62" width="13.7109375" style="4" customWidth="1"/>
-    <col min="63" max="63" width="9.140625" style="4"/>
+    <col min="63" max="63" width="0" style="4" hidden="1" customWidth="1"/>
     <col min="64" max="65" width="14" style="4" customWidth="1"/>
-    <col min="66" max="16384" width="9.140625" style="4"/>
+    <col min="66" max="66" width="9.140625" style="4"/>
+    <col min="67" max="67" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="68" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:80" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4">
         <v>1</v>
       </c>
@@ -1682,14 +1742,14 @@
       <c r="AS1" s="4"/>
       <c r="AW1" s="4"/>
     </row>
-    <row r="2" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:80" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="K2" s="93" t="s">
+      <c r="K2" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="93"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="54">
         <f>BQ14</f>
         <v>0</v>
@@ -1708,7 +1768,7 @@
       <c r="AS2" s="4"/>
       <c r="AW2" s="4"/>
     </row>
-    <row r="3" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:80" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3</v>
       </c>
@@ -1726,7 +1786,7 @@
       <c r="AS3" s="4"/>
       <c r="AW3" s="4"/>
     </row>
-    <row r="4" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:80" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>4</v>
       </c>
@@ -1744,25 +1804,163 @@
       <c r="AS4" s="4"/>
       <c r="AW4" s="4"/>
     </row>
-    <row r="5" spans="1:79" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:80" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>5</v>
       </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="U5" s="4"/>
-      <c r="V5" s="64"/>
-      <c r="AE5" s="4"/>
-      <c r="AI5" s="4"/>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="4"/>
-      <c r="AL5" s="4"/>
-      <c r="AM5" s="4"/>
-      <c r="AN5" s="4"/>
+      <c r="V5" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="AQ5" s="4"/>
       <c r="AS5" s="4"/>
-      <c r="AW5" s="4"/>
+      <c r="AT5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AW5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="BA5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BH5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI5" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="BK5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="BO5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="BP5" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="BQ5" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="BR5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="BS5" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="BT5" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="BU5" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="BW5" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="BX5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="BY5" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="BZ5" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="CA5" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
-    <row r="6" spans="1:79" ht="24.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:80" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>6</v>
       </c>
@@ -1921,8 +2119,11 @@
       <c r="CA6" s="4" t="s">
         <v>89</v>
       </c>
+      <c r="CB6" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
-    <row r="7" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:80" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>7</v>
       </c>
@@ -2060,7 +2261,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:80" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>8</v>
       </c>
@@ -2090,7 +2291,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:80" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>9</v>
       </c>
@@ -2234,7 +2435,7 @@
       </c>
       <c r="AW9" s="4"/>
     </row>
-    <row r="10" spans="1:79" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:80" ht="24.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>10</v>
       </c>
@@ -2360,102 +2561,102 @@
       </c>
       <c r="AW10" s="4"/>
     </row>
-    <row r="11" spans="1:79" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="77" t="s">
+    <row r="11" spans="1:80" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="77" t="s">
+      <c r="E11" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="96" t="s">
+      <c r="G11" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="98" t="s">
+      <c r="H11" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72" t="s">
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="72"/>
-      <c r="P11" s="73" t="s">
+      <c r="O11" s="84"/>
+      <c r="P11" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="75" t="s">
+      <c r="Q11" s="96"/>
+      <c r="R11" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="S11" s="76"/>
-      <c r="T11" s="72" t="s">
+      <c r="S11" s="98"/>
+      <c r="T11" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="72"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="77" t="s">
+      <c r="U11" s="84"/>
+      <c r="V11" s="84"/>
+      <c r="W11" s="84"/>
+      <c r="X11" s="84"/>
+      <c r="Y11" s="84"/>
+      <c r="Z11" s="84"/>
+      <c r="AA11" s="84"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="84"/>
+      <c r="AD11" s="84"/>
+      <c r="AE11" s="84"/>
+      <c r="AF11" s="84"/>
+      <c r="AG11" s="84"/>
+      <c r="AH11" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="AI11" s="67" t="s">
+      <c r="AI11" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="AJ11" s="67"/>
-      <c r="AK11" s="67"/>
-      <c r="AL11" s="67"/>
-      <c r="AM11" s="67"/>
-      <c r="AN11" s="67"/>
-      <c r="AO11" s="67"/>
-      <c r="AP11" s="68" t="s">
+      <c r="AJ11" s="90"/>
+      <c r="AK11" s="90"/>
+      <c r="AL11" s="90"/>
+      <c r="AM11" s="90"/>
+      <c r="AN11" s="90"/>
+      <c r="AO11" s="90"/>
+      <c r="AP11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="AQ11" s="70" t="s">
+      <c r="AQ11" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="AR11" s="71"/>
-      <c r="AS11" s="71"/>
-      <c r="AT11" s="71"/>
-      <c r="AU11" s="71"/>
-      <c r="AV11" s="82" t="s">
+      <c r="AR11" s="94"/>
+      <c r="AS11" s="94"/>
+      <c r="AT11" s="94"/>
+      <c r="AU11" s="94"/>
+      <c r="AV11" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="AW11" s="70" t="s">
+      <c r="AW11" s="93" t="s">
         <v>154</v>
       </c>
-      <c r="AX11" s="82" t="s">
+      <c r="AX11" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="AY11" s="82" t="s">
+      <c r="AY11" s="67" t="s">
         <v>16</v>
       </c>
       <c r="AZ11" s="7"/>
-      <c r="BA11" s="100" t="s">
+      <c r="BA11" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="BB11" s="102" t="s">
+      <c r="BB11" s="73" t="s">
         <v>18</v>
       </c>
       <c r="BC11" s="8"/>
@@ -2470,58 +2671,61 @@
       <c r="BI11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BJ11" s="87" t="s">
+      <c r="BJ11" s="102" t="s">
         <v>161</v>
       </c>
-      <c r="BK11" s="79" t="s">
+      <c r="BK11" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="BL11" s="79" t="s">
+      <c r="BL11" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="BM11" s="84" t="s">
+      <c r="BM11" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="BN11" s="85"/>
+      <c r="BN11" s="101"/>
       <c r="BO11" s="66"/>
-      <c r="BP11" s="79" t="s">
+      <c r="BP11" s="71" t="s">
         <v>144</v>
       </c>
       <c r="BQ11" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="BR11" s="79" t="s">
+      <c r="BR11" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="BS11" s="91" t="s">
+      <c r="BS11" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="BT11" s="91"/>
+      <c r="BT11" s="88"/>
       <c r="BU11" s="86" t="s">
         <v>59</v>
       </c>
       <c r="BV11" s="86"/>
-      <c r="BW11" s="92" t="s">
+      <c r="BW11" s="89" t="s">
         <v>159</v>
       </c>
-      <c r="BX11" s="90" t="s">
+      <c r="BX11" s="87" t="s">
         <v>151</v>
       </c>
-      <c r="BY11" s="89" t="s">
+      <c r="BY11" s="85" t="s">
         <v>152</v>
       </c>
-      <c r="CA11" s="89" t="s">
+      <c r="CA11" s="85" t="s">
         <v>90</v>
       </c>
+      <c r="CB11" s="85" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="12" spans="1:79" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="95"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="99"/>
+    <row r="12" spans="1:80" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="77"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="83"/>
       <c r="I12" s="48" t="s">
         <v>20</v>
       </c>
@@ -2597,7 +2801,7 @@
       <c r="AG12" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="AH12" s="78"/>
+      <c r="AH12" s="79"/>
       <c r="AI12" s="49">
         <v>1.5</v>
       </c>
@@ -2619,7 +2823,7 @@
       <c r="AO12" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AP12" s="69"/>
+      <c r="AP12" s="92"/>
       <c r="AQ12" s="46" t="s">
         <v>42</v>
       </c>
@@ -2635,13 +2839,13 @@
       <c r="AU12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="AV12" s="83"/>
-      <c r="AW12" s="81"/>
-      <c r="AX12" s="83"/>
-      <c r="AY12" s="83"/>
+      <c r="AV12" s="68"/>
+      <c r="AW12" s="99"/>
+      <c r="AX12" s="68"/>
+      <c r="AY12" s="68"/>
       <c r="AZ12" s="9"/>
-      <c r="BA12" s="101"/>
-      <c r="BB12" s="103"/>
+      <c r="BA12" s="70"/>
+      <c r="BB12" s="74"/>
       <c r="BC12" s="10" t="str">
         <f>+IF(C12="SK2","SK2",IF(C12="FACTORY A","SK1 Box",IF(C12="FACTORY D","SK1 Bag","Chia")))</f>
         <v>Chia</v>
@@ -2651,9 +2855,9 @@
         <f>+IF(BC12="SK1 Box","Box",IF(BC12="Seaman","Seaman","Bag"))</f>
         <v>Bag</v>
       </c>
-      <c r="BJ12" s="88"/>
-      <c r="BK12" s="80"/>
-      <c r="BL12" s="80"/>
+      <c r="BJ12" s="103"/>
+      <c r="BK12" s="72"/>
+      <c r="BL12" s="72"/>
       <c r="BM12" s="35" t="s">
         <v>91</v>
       </c>
@@ -2663,9 +2867,9 @@
       <c r="BO12" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="BP12" s="80"/>
+      <c r="BP12" s="72"/>
       <c r="BQ12" s="86"/>
-      <c r="BR12" s="80"/>
+      <c r="BR12" s="72"/>
       <c r="BS12" s="34">
         <v>1</v>
       </c>
@@ -2678,15 +2882,16 @@
       <c r="BV12" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="BW12" s="92"/>
-      <c r="BX12" s="90"/>
-      <c r="BY12" s="89"/>
+      <c r="BW12" s="89"/>
+      <c r="BX12" s="87"/>
+      <c r="BY12" s="85"/>
       <c r="BZ12" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="CA12" s="89"/>
+      <c r="CA12" s="85"/>
+      <c r="CB12" s="85"/>
     </row>
-    <row r="13" spans="1:79" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:80" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>1</v>
       </c>
@@ -2887,7 +3092,7 @@
       <c r="BD13" s="16"/>
       <c r="BE13" s="17"/>
     </row>
-    <row r="14" spans="1:79" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:80" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="18">
         <f>SUBTOTAL(3,C$14:C14)</f>
         <v>0</v>
@@ -2934,9 +3139,9 @@
         <f>(BT14)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="23">
+      <c r="S14" s="23" t="e">
         <f>ROUND(BJ14/8*BT14*0.3,0)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="T14" s="23" t="e">
         <f>O14+Q14+S14</f>
@@ -2968,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="23" t="e">
-        <f>ROUND(M14/IF($M$2&gt;26,26,BQ14)*AB14,0)</f>
+        <f>IF(CB14&gt;=1,CB14,ROUND(M14/IF($M$2&gt;26,26,BQ14)*AB14,0))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD14" s="27">
@@ -3006,9 +3211,9 @@
       <c r="AN14" s="24">
         <v>0</v>
       </c>
-      <c r="AO14" s="50">
+      <c r="AO14" s="50" t="e">
         <f>ROUND(BJ14/8*(AI14*1.5 + AJ14* 2 + AK14* 2.1 + AL14* 2.7 + AM14* 3 + AN14* 3.9),0)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AP14" s="31" t="e">
         <f>ROUND(AH14+AO14,0)</f>
@@ -3023,8 +3228,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AS14" s="51" t="e">
-        <f>IF(#REF!=1,IF(BL14&gt;11000000,BL14*10%,0),IF(BM14&gt;0,ROUND(IF(BM14&lt;5000000,BM14*0.05,IF(BM14&lt;10000000,BM14*0.1-250000,IF(BM14&lt;18000000,BM14*0.15-750000,IF(BM14&lt;32000000,BM14*0.2-1650000,IF(BM14&lt;52000000,BM14*0.25-3250000,IF(BM14&lt;80000000,BM14*0.3-5850000,BM14*0.35-9850000)))))),0),0))</f>
-        <v>#REF!</v>
+        <f>IF(BO14=1,IF(BL14&gt;11000000,BL14*10%,0),IF(BM14&gt;0,ROUND(IF(BM14&lt;5000000,BM14*0.05,IF(BM14&lt;10000000,BM14*0.1-250000,IF(BM14&lt;18000000,BM14*0.15-750000,IF(BM14&lt;32000000,BM14*0.2-1650000,IF(BM14&lt;52000000,BM14*0.25-3250000,IF(BM14&lt;80000000,BM14*0.3-5850000,BM14*0.35-9850000)))))),0),0))</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="AT14" s="23">
         <v>0</v>
@@ -3059,9 +3264,9 @@
       <c r="BG14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BJ14" s="4">
-        <f>IF(N14&gt;0,O14/IF(N14&gt;26,26,N14),0)</f>
-        <v>0</v>
+      <c r="BJ14" s="4" t="e">
+        <f>M14/IF($M$2&gt;26,26,$M$2)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="BK14" s="4">
         <v>0</v>
@@ -3070,8 +3275,8 @@
         <f>AP14 + BP14 - AQ14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BM14" s="104" t="e">
-        <f>BL14-#REF!-U14-BN14*4400000-11000000 - ROUND(BJ14/8*(BT14*0.3+AI14*0.5+AJ14*1+AK14*1.1+AL14*1.7+AM14*2+AN14*2.9),0)</f>
+      <c r="BM14" s="4" t="e">
+        <f>BL14-U14-BN14*4400000-11000000 - ROUND(BJ14/8*(BT14*0.3+AI14*0.5+AJ14*1+AK14*1.1+AL14*1.7+AM14*2+AN14*2.9),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BN14" s="4">
@@ -3109,18 +3314,37 @@
         <v>0</v>
       </c>
       <c r="CA14" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB14" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A13:BE13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="36">
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AY11:AY12"/>
-    <mergeCell ref="BA11:BA12"/>
-    <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BB11:BB12"/>
-    <mergeCell ref="BK11:BK12"/>
+  <mergeCells count="37">
+    <mergeCell ref="CB11:CB12"/>
+    <mergeCell ref="AI11:AO11"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AU11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:AG11"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="BR11:BR12"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="AX11:AX12"/>
+    <mergeCell ref="BM11:BN11"/>
+    <mergeCell ref="BL11:BL12"/>
+    <mergeCell ref="BQ11:BQ12"/>
+    <mergeCell ref="BJ11:BJ12"/>
+    <mergeCell ref="CA11:CA12"/>
+    <mergeCell ref="BU11:BV11"/>
+    <mergeCell ref="BY11:BY12"/>
+    <mergeCell ref="BX11:BX12"/>
+    <mergeCell ref="BS11:BT11"/>
+    <mergeCell ref="BW11:BW12"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
@@ -3130,27 +3354,12 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:M11"/>
-    <mergeCell ref="CA11:CA12"/>
-    <mergeCell ref="BU11:BV11"/>
-    <mergeCell ref="BY11:BY12"/>
-    <mergeCell ref="BX11:BX12"/>
-    <mergeCell ref="BS11:BT11"/>
-    <mergeCell ref="BW11:BW12"/>
-    <mergeCell ref="BR11:BR12"/>
-    <mergeCell ref="AW11:AW12"/>
-    <mergeCell ref="AX11:AX12"/>
-    <mergeCell ref="BM11:BN11"/>
-    <mergeCell ref="BL11:BL12"/>
-    <mergeCell ref="BQ11:BQ12"/>
-    <mergeCell ref="BJ11:BJ12"/>
-    <mergeCell ref="AI11:AO11"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AU11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:AG11"/>
-    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AY11:AY12"/>
+    <mergeCell ref="BA11:BA12"/>
+    <mergeCell ref="BP11:BP12"/>
+    <mergeCell ref="BB11:BB12"/>
+    <mergeCell ref="BK11:BK12"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C11:C13 D13:AY13">
